--- a/Power_Systems_Comparison.xlsx
+++ b/Power_Systems_Comparison.xlsx
@@ -941,7 +941,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="36294060" cy="26951940"/>
+    <ext cx="36294060" cy="27020520"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -2420,7 +2420,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>- Report Generated: October 29, 2025</t>
+          <t>- Report Generated: October 30, 2025</t>
         </is>
       </c>
     </row>

--- a/Power_Systems_Comparison.xlsx
+++ b/Power_Systems_Comparison.xlsx
@@ -610,7 +610,7 @@
           <idx val="1"/>
           <order val="1"/>
           <tx>
-            <v>Caterpillar Op. Margin</v>
+            <v>Caterpillar EBITDA Margin</v>
           </tx>
           <spPr>
             <a:ln w="38100">
@@ -663,22 +663,22 @@
                 <formatCode>General</formatCode>
                 <ptCount val="6"/>
                 <pt idx="0">
-                  <v>0.1</v>
+                  <v>0.145</v>
                 </pt>
                 <pt idx="1">
-                  <v>0.109</v>
+                  <v>0.164</v>
                 </pt>
                 <pt idx="2">
-                  <v>0.115</v>
+                  <v>0.161</v>
                 </pt>
                 <pt idx="3">
-                  <v>0.159</v>
+                  <v>0.198</v>
                 </pt>
                 <pt idx="4">
-                  <v>0.19</v>
+                  <v>0.222</v>
                 </pt>
                 <pt idx="5">
-                  <v>0.199</v>
+                  <v>0.233</v>
                 </pt>
               </numCache>
             </numRef>
@@ -941,7 +941,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="36294060" cy="27020520"/>
+    <ext cx="36301680" cy="27020520"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>CAT Op. Profit ($M)</t>
+          <t>CAT EBITDA ($M)</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1427,10 +1427,10 @@
         <v>20870</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>2088</v>
+        <v>3019</v>
       </c>
       <c r="G4" s="9" t="n">
-        <v>0.1</v>
+        <v>0.145</v>
       </c>
     </row>
     <row r="5">
@@ -1450,10 +1450,10 @@
         <v>19231</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>2100</v>
+        <v>3159</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>0.109</v>
+        <v>0.164</v>
       </c>
     </row>
     <row r="6">
@@ -1473,10 +1473,10 @@
         <v>22831</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>2623</v>
+        <v>3677</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>0.115</v>
+        <v>0.161</v>
       </c>
     </row>
     <row r="7">
@@ -1496,10 +1496,10 @@
         <v>26330</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>4184</v>
+        <v>5225</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>0.159</v>
+        <v>0.198</v>
       </c>
     </row>
     <row r="8">
@@ -1519,10 +1519,10 @@
         <v>28000</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>5310</v>
+        <v>6205</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>0.19</v>
+        <v>0.222</v>
       </c>
     </row>
     <row r="9">
@@ -1542,10 +1542,10 @@
         <v>28850</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>5750</v>
+        <v>6708</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>0.199</v>
+        <v>0.233</v>
       </c>
     </row>
   </sheetData>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Operating Profit ($M)</t>
+          <t>EBITDA ($M)</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Op. Margin (%)</t>
+          <t>EBITDA Margin (%)</t>
         </is>
       </c>
     </row>
@@ -1666,10 +1666,10 @@
         <v>30450</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>6054</v>
+        <v>7046</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.199</v>
+        <v>0.231</v>
       </c>
     </row>
     <row r="11">
@@ -1723,30 +1723,30 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Profit ($B)</t>
+          <t>EBITDA ($B)</t>
         </is>
       </c>
       <c r="B14" s="12" t="n">
         <v>1.46</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>6.05</v>
+        <v>7.05</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Margin (%)</t>
+          <t>EBITDA Margin (%)</t>
         </is>
       </c>
       <c r="B15" s="9" t="n">
         <v>0.212</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>0.199</v>
+        <v>0.231</v>
       </c>
       <c r="D15" s="9" t="n"/>
     </row>
@@ -2147,7 +2147,7 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>4. PROFITABILITY (2024)</t>
+          <t>4. PROFITABILITY (2024 - Apples-to-Apples EBITDA)</t>
         </is>
       </c>
       <c r="B17" s="6" t="n"/>
@@ -2167,24 +2167,24 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Caterpillar Operating Margin</t>
+          <t xml:space="preserve">   Caterpillar EBITDA Margin</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>23.3%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Difference</t>
+          <t xml:space="preserve">   Caterpillar leads</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0.2 pts</t>
+          <t>+3.6 pts</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>+9.9 percentage points (10.0% → 19.9%)</t>
+          <t>+8.8 percentage points (14.5% → 23.3%)</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>6. LTM PROFITABILITY (Most Recent)</t>
+          <t>6. LTM PROFITABILITY (Most Recent - EBITDA)</t>
         </is>
       </c>
       <c r="B26" s="6" t="n"/>
@@ -2251,24 +2251,24 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Caterpillar LTM Margin</t>
+          <t xml:space="preserve">   Caterpillar LTM EBITDA Margin</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>23.1%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Cummins now leads in margin</t>
+          <t xml:space="preserve">   Caterpillar maintains lead</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>+1.3 pts</t>
+          <t>+1.9 pts</t>
         </is>
       </c>
     </row>
@@ -2279,7 +2279,7 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>7. PROFIT DOLLARS (LTM)</t>
+          <t>7. EBITDA DOLLARS (LTM)</t>
         </is>
       </c>
       <c r="B31" s="6" t="n"/>
@@ -2287,12 +2287,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Caterpillar Operating Profit</t>
+          <t xml:space="preserve">   Caterpillar EBITDA</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>$6.05 Billion</t>
+          <t>$7.05 Billion</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>4.1x</t>
+          <t>4.8x</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Larger, more diversified, stable leader</t>
+          <t>Larger (4.4x), higher EBITDA margin leader</t>
         </is>
       </c>
     </row>
@@ -2392,7 +2392,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Faster growth, superior margin expansion</t>
+          <t>Faster growth, rapidly closing margin gap</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>- Note: Caterpillar reports Operating Profit; Cummins reports EBITDA</t>
+          <t>- APPLES-TO-APPLES: Both showing EBITDA. CAT EBITDA = Op. Profit + allocated D&amp;A</t>
         </is>
       </c>
     </row>
